--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -35216,13 +35216,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>1683</v>
+        <v>1697</v>
       </c>
       <c r="O188" t="n">
-        <v>1683</v>
+        <v>1697</v>
       </c>
       <c r="R188" t="n">
-        <v>3.261603381742013</v>
+        <v>3.288734960675102</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -39083,13 +39083,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="O208" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="R208" t="n">
-        <v>0.1608515036747398</v>
+        <v>0.2616259397119262</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>377807</v>
+        <v>377873</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -38651,12 +38651,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -38681,104 +38681,112 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N206" t="n">
+        <v>433</v>
+      </c>
+      <c r="O206" t="n">
+        <v>433</v>
+      </c>
+      <c r="P206" t="n">
+        <v>433</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.3536780404759768</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
         <v>2</v>
       </c>
-      <c r="O206" t="n">
-        <v>2</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0.007345623639039581</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO206" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP206" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="AT206" t="n">
-        <v>1</v>
-      </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38810,12 +38818,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38840,179 +38848,187 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N207" t="n">
+        <v>9</v>
+      </c>
+      <c r="O207" t="n">
+        <v>9</v>
+      </c>
+      <c r="P207" t="n">
+        <v>9</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT207" t="n">
         <v>2</v>
       </c>
-      <c r="O207" t="n">
-        <v>2</v>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Varicella zoster (chickenpox)</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO207" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP207" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="AT207" t="n">
-        <v>1</v>
-      </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39039,123 +39055,758 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>433</v>
+      </c>
+      <c r="O208" t="n">
+        <v>433</v>
+      </c>
+      <c r="P208" t="n">
+        <v>433</v>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>2</v>
+      </c>
+      <c r="O209" t="n">
+        <v>2</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="AT209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N210" t="n">
+        <v>2</v>
+      </c>
+      <c r="O210" t="n">
+        <v>2</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Varicella zoster (chickenpox)</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="AT210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA210" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>D054</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>Varicella</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
         <is>
           <t>水痘</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="K211" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N208" t="n">
+      <c r="N211" t="n">
         <v>135</v>
       </c>
-      <c r="O208" t="n">
+      <c r="O211" t="n">
         <v>135</v>
       </c>
-      <c r="R208" t="n">
+      <c r="R211" t="n">
         <v>0.2616259397119262</v>
       </c>
-      <c r="S208" t="inlineStr">
+      <c r="S211" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO208" t="inlineStr">
+      <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP208" t="inlineStr">
+      <c r="AP211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR208" t="inlineStr">
+      <c r="AR211" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS208" t="inlineStr"/>
-      <c r="AT208" t="n">
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="n">
         <v>0</v>
       </c>
-      <c r="AU208" t="inlineStr">
+      <c r="AU211" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV208" t="inlineStr">
+      <c r="AV211" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW208" t="inlineStr">
+      <c r="AW211" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX208" t="inlineStr">
+      <c r="AX211" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY208" t="inlineStr">
+      <c r="AY211" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ208" t="inlineStr">
+      <c r="AZ211" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA208" t="inlineStr">
+      <c r="BA211" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB208" t="inlineStr">
+      <c r="BB211" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC208" t="inlineStr">
+      <c r="BC211" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -39277,7 +39928,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -39287,7 +39938,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -39307,7 +39958,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -39339,7 +39990,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>377873</v>
+        <v>378306</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -30500,13 +30500,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="O162" t="n">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="R162" t="n">
-        <v>4.873994358336995</v>
+        <v>4.86818044856562</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -35216,13 +35216,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>1697</v>
+        <v>1744</v>
       </c>
       <c r="O188" t="n">
-        <v>1697</v>
+        <v>1744</v>
       </c>
       <c r="R188" t="n">
-        <v>3.288734960675102</v>
+        <v>3.379819547093328</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -39734,13 +39734,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>135</v>
+        <v>347</v>
       </c>
       <c r="O211" t="n">
-        <v>135</v>
+        <v>347</v>
       </c>
       <c r="R211" t="n">
-        <v>0.2616259397119262</v>
+        <v>0.6724755635558399</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -39990,7 +39990,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>378306</v>
+        <v>378562</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -23530,7 +23530,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -29071,7 +29071,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -33829,13 +33829,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="O179" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="R179" t="n">
-        <v>0.3746268055910186</v>
+        <v>0.6868158102502008</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -33988,10 +33988,10 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="O180" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -35177,12 +35177,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -35216,13 +35216,16 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>1744</v>
+        <v>30758</v>
       </c>
       <c r="O188" t="n">
-        <v>1744</v>
+        <v>30758</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>3.379819547093328</v>
+        <v>2.17691933645122</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -35255,42 +35258,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -35322,12 +35325,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -35361,13 +35364,13 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>37</v>
+        <v>1744</v>
       </c>
       <c r="O189" t="n">
-        <v>37</v>
+        <v>1744</v>
       </c>
       <c r="R189" t="n">
-        <v>0.01060064109124673</v>
+        <v>3.379819547093328</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -35400,42 +35403,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35467,12 +35470,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35497,7 +35500,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -35506,103 +35509,81 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>594</v>
+        <v>37</v>
       </c>
       <c r="O190" t="n">
-        <v>594</v>
-      </c>
-      <c r="P190" t="n">
-        <v>594</v>
+        <v>37</v>
       </c>
       <c r="R190" t="n">
-        <v>0.4851841940940652</v>
+        <v>0.01060064109124673</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35629,7 +35610,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -35673,106 +35654,31 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>19</v>
+        <v>594</v>
       </c>
       <c r="O191" t="n">
-        <v>19</v>
+        <v>594</v>
       </c>
       <c r="P191" t="n">
-        <v>19</v>
+        <v>594</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0.4851841940940652</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN191" t="b">
-        <v>0</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -35915,22 +35821,22 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="O192" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="P192" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
@@ -35940,17 +35846,17 @@
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -36005,7 +35911,7 @@
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
@@ -36014,7 +35920,7 @@
         </is>
       </c>
       <c r="AN192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -36113,17 +36019,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -36148,7 +36054,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -36157,81 +36063,178 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>41</v>
+        <v>594</v>
       </c>
       <c r="O193" t="n">
-        <v>41</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0.01174665634435448</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>594</v>
+      </c>
+      <c r="P193" t="n">
+        <v>594</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR193" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36263,12 +36266,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -36293,7 +36296,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -36302,103 +36305,81 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>555</v>
+        <v>41</v>
       </c>
       <c r="O194" t="n">
-        <v>555</v>
-      </c>
-      <c r="P194" t="n">
-        <v>555</v>
+        <v>41</v>
       </c>
       <c r="R194" t="n">
-        <v>0.4533286661990003</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36425,7 +36406,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -36469,106 +36450,31 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>11</v>
+        <v>555</v>
       </c>
       <c r="O195" t="n">
-        <v>11</v>
+        <v>555</v>
       </c>
       <c r="P195" t="n">
-        <v>11</v>
+        <v>555</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0.4533286661990003</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>0</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -36711,22 +36617,22 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="O196" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="P196" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
@@ -36736,17 +36642,17 @@
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -36801,7 +36707,7 @@
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM196" t="inlineStr">
@@ -36810,7 +36716,7 @@
         </is>
       </c>
       <c r="AN196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -36909,17 +36815,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36944,7 +36850,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -36953,81 +36859,178 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>38</v>
+        <v>555</v>
       </c>
       <c r="O197" t="n">
-        <v>38</v>
-      </c>
-      <c r="R197" t="n">
-        <v>0.01088714490452366</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>555</v>
+      </c>
+      <c r="P197" t="n">
+        <v>555</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37059,12 +37062,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -37089,7 +37092,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -37098,103 +37101,81 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="O198" t="n">
-        <v>386</v>
-      </c>
-      <c r="P198" t="n">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="R198" t="n">
-        <v>0.3152880453203858</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37221,7 +37202,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -37265,106 +37246,31 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>12</v>
+        <v>386</v>
       </c>
       <c r="O199" t="n">
-        <v>12</v>
+        <v>386</v>
       </c>
       <c r="P199" t="n">
-        <v>12</v>
+        <v>386</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0.3152880453203858</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
-        <v>0</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -37507,22 +37413,22 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>386</v>
+        <v>12</v>
       </c>
       <c r="O200" t="n">
-        <v>386</v>
+        <v>12</v>
       </c>
       <c r="P200" t="n">
-        <v>386</v>
+        <v>12</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
@@ -37532,17 +37438,17 @@
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -37597,7 +37503,7 @@
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
@@ -37606,7 +37512,7 @@
         </is>
       </c>
       <c r="AN200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -37705,17 +37611,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -37740,7 +37646,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -37749,81 +37655,178 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>43</v>
+        <v>386</v>
       </c>
       <c r="O201" t="n">
-        <v>43</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0.01231966397090836</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>386</v>
+      </c>
+      <c r="P201" t="n">
+        <v>386</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37855,12 +37858,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37885,7 +37888,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -37894,103 +37897,81 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>589</v>
+        <v>43</v>
       </c>
       <c r="O202" t="n">
-        <v>589</v>
-      </c>
-      <c r="P202" t="n">
-        <v>589</v>
+        <v>43</v>
       </c>
       <c r="R202" t="n">
-        <v>0.4811001520562364</v>
+        <v>0.01231966397090836</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38017,7 +37998,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -38061,106 +38042,31 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>11</v>
+        <v>589</v>
       </c>
       <c r="O203" t="n">
-        <v>11</v>
+        <v>589</v>
       </c>
       <c r="P203" t="n">
-        <v>11</v>
+        <v>589</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0.4811001520562364</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>0</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -38303,22 +38209,22 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>589</v>
+        <v>11</v>
       </c>
       <c r="O204" t="n">
-        <v>589</v>
+        <v>11</v>
       </c>
       <c r="P204" t="n">
-        <v>589</v>
+        <v>11</v>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
@@ -38328,17 +38234,17 @@
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -38393,7 +38299,7 @@
       </c>
       <c r="AK204" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM204" t="inlineStr">
@@ -38402,7 +38308,7 @@
         </is>
       </c>
       <c r="AN204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -38501,17 +38407,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -38536,7 +38442,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -38545,81 +38451,178 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>38</v>
+        <v>589</v>
       </c>
       <c r="O205" t="n">
-        <v>38</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0.01088714490452366</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>589</v>
+      </c>
+      <c r="P205" t="n">
+        <v>589</v>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR205" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38651,12 +38654,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -38681,7 +38684,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -38690,103 +38693,81 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>433</v>
+        <v>38</v>
       </c>
       <c r="O206" t="n">
-        <v>433</v>
-      </c>
-      <c r="P206" t="n">
-        <v>433</v>
+        <v>38</v>
       </c>
       <c r="R206" t="n">
-        <v>0.3536780404759768</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38794,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -38857,106 +38838,31 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>9</v>
+        <v>433</v>
       </c>
       <c r="O207" t="n">
-        <v>9</v>
+        <v>433</v>
       </c>
       <c r="P207" t="n">
-        <v>9</v>
+        <v>433</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0.3536780404759768</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>0</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -39099,22 +39005,22 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>433</v>
+        <v>9</v>
       </c>
       <c r="O208" t="n">
-        <v>433</v>
+        <v>9</v>
       </c>
       <c r="P208" t="n">
-        <v>433</v>
+        <v>9</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
@@ -39124,17 +39030,17 @@
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -39189,7 +39095,7 @@
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -39198,7 +39104,7 @@
         </is>
       </c>
       <c r="AN208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -39297,17 +39203,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -39332,104 +39238,187 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N209" t="n">
+        <v>433</v>
+      </c>
+      <c r="O209" t="n">
+        <v>433</v>
+      </c>
+      <c r="P209" t="n">
+        <v>433</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT209" t="n">
         <v>2</v>
       </c>
-      <c r="O209" t="n">
-        <v>2</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0.007345623639039581</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO209" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP209" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="AT209" t="n">
-        <v>1</v>
-      </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39456,7 +39445,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -39505,98 +39494,23 @@
       <c r="O210" t="n">
         <v>2</v>
       </c>
+      <c r="R210" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U210" t="inlineStr">
         <is>
           <t>SER_AU_VARICELLA_CHICKENPOX</t>
         </is>
       </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Varicella zoster (chickenpox)</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -39690,125 +39604,504 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>2</v>
+      </c>
+      <c r="O211" t="n">
+        <v>2</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Varicella zoster (chickenpox)</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>D054</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>Varicella</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
         <is>
           <t>水痘</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="K212" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N211" t="n">
+      <c r="N212" t="n">
         <v>347</v>
       </c>
-      <c r="O211" t="n">
+      <c r="O212" t="n">
         <v>347</v>
       </c>
-      <c r="R211" t="n">
+      <c r="R212" t="n">
         <v>0.6724755635558399</v>
       </c>
-      <c r="S211" t="inlineStr">
+      <c r="S212" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO211" t="inlineStr">
+      <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP211" t="inlineStr">
+      <c r="AP212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR211" t="inlineStr">
+      <c r="AR212" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS211" t="inlineStr"/>
-      <c r="AT211" t="n">
+      <c r="AS212" t="inlineStr"/>
+      <c r="AT212" t="n">
         <v>0</v>
       </c>
-      <c r="AU211" t="inlineStr">
+      <c r="AU212" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV211" t="inlineStr">
+      <c r="AV212" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW211" t="inlineStr">
+      <c r="AW212" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX211" t="inlineStr">
+      <c r="AX212" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY211" t="inlineStr">
+      <c r="AY212" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ211" t="inlineStr">
+      <c r="AZ212" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA211" t="inlineStr">
+      <c r="BA212" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB211" t="inlineStr">
+      <c r="BB212" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC211" t="inlineStr">
+      <c r="BC212" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>41</v>
+      </c>
+      <c r="O213" t="n">
+        <v>41</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.01174665634435448</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39845,7 +40138,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -39928,7 +40221,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -39938,7 +40231,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -39990,7 +40283,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>378562</v>
+        <v>409446</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -30168,12 +30168,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -30207,84 +30207,92 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>46105</v>
+        <v>72</v>
       </c>
       <c r="O160" t="n">
-        <v>46105</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="R160" t="n">
-        <v>3.263114181906609</v>
+        <v>72</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30311,17 +30319,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -30355,81 +30363,170 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="O161" t="n">
-        <v>136</v>
-      </c>
-      <c r="R161" t="n">
-        <v>1.843167581067525</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>72</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Chickenpox (Varicella)</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary chickenpox (varicella) notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VARICELLA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30461,12 +30558,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -30500,13 +30597,16 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>2512</v>
+        <v>46105</v>
       </c>
       <c r="O162" t="n">
-        <v>2512</v>
+        <v>46105</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>4.86818044856562</v>
+        <v>3.263114181906609</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -30539,42 +30639,42 @@
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -30606,12 +30706,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -30636,7 +30736,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -30645,13 +30745,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="O163" t="n">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="R163" t="n">
-        <v>0.007449099145200401</v>
+        <v>1.843167581067525</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -30684,42 +30784,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -30751,12 +30851,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -30781,7 +30881,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -30790,103 +30890,81 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>719</v>
+        <v>2512</v>
       </c>
       <c r="O164" t="n">
-        <v>719</v>
-      </c>
-      <c r="P164" t="n">
-        <v>719</v>
+        <v>2512</v>
       </c>
       <c r="R164" t="n">
-        <v>0.587285245039786</v>
+        <v>4.86818044856562</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -30913,17 +30991,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -30948,7 +31026,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -30957,178 +31035,81 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="O165" t="n">
-        <v>15</v>
-      </c>
-      <c r="P165" t="n">
-        <v>15</v>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
+        <v>26</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.007449099145200401</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
         <v>0</v>
       </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP165" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT165" t="n">
-        <v>2</v>
-      </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31155,7 +31136,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -31207,98 +31188,23 @@
       <c r="P166" t="n">
         <v>719</v>
       </c>
+      <c r="R166" t="n">
+        <v>0.587285245039786</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U166" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -31397,17 +31303,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -31432,7 +31338,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -31441,81 +31347,178 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="O167" t="n">
-        <v>43</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0.01231966397090836</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="P167" t="n">
+        <v>15</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>0</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31542,7 +31545,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -31577,7 +31580,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -31586,31 +31589,106 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>867</v>
+        <v>719</v>
       </c>
       <c r="O168" t="n">
-        <v>867</v>
+        <v>719</v>
       </c>
       <c r="P168" t="n">
-        <v>867</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0.7081728893595194</v>
-      </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>719</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN168" t="b">
+        <v>1</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -31709,17 +31787,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -31744,7 +31822,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -31753,178 +31831,81 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="O169" t="n">
-        <v>11</v>
-      </c>
-      <c r="P169" t="n">
-        <v>11</v>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN169" t="b">
+        <v>43</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.01231966397090836</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
         <v>0</v>
       </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP169" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT169" t="n">
-        <v>2</v>
-      </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31951,7 +31932,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -32003,98 +31984,23 @@
       <c r="P170" t="n">
         <v>867</v>
       </c>
+      <c r="R170" t="n">
+        <v>0.7081728893595194</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN170" t="b">
-        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
@@ -32193,17 +32099,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -32228,7 +32134,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -32237,81 +32143,178 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="O171" t="n">
-        <v>29</v>
-      </c>
-      <c r="R171" t="n">
-        <v>0.008308610585031217</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="P171" t="n">
+        <v>11</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>0</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32338,7 +32341,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -32373,7 +32376,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -32382,31 +32385,106 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>669</v>
+        <v>867</v>
       </c>
       <c r="O172" t="n">
-        <v>669</v>
+        <v>867</v>
       </c>
       <c r="P172" t="n">
-        <v>669</v>
-      </c>
-      <c r="R172" t="n">
-        <v>0.5464448246614977</v>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>867</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
+        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -32505,17 +32583,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -32540,7 +32618,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -32549,178 +32627,81 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="O173" t="n">
-        <v>13</v>
-      </c>
-      <c r="P173" t="n">
-        <v>13</v>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W173" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD173" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE173" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF173" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG173" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM173" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN173" t="b">
+        <v>29</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.008308610585031217</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="n">
         <v>0</v>
       </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP173" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT173" t="n">
-        <v>2</v>
-      </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32747,7 +32728,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -32799,98 +32780,23 @@
       <c r="P174" t="n">
         <v>669</v>
       </c>
+      <c r="R174" t="n">
+        <v>0.5464448246614977</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN174" t="b">
-        <v>1</v>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
@@ -32989,17 +32895,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -33024,7 +32930,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -33033,81 +32939,178 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="O175" t="n">
-        <v>32</v>
-      </c>
-      <c r="R175" t="n">
-        <v>0.009168122024862033</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="P175" t="n">
+        <v>13</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>0</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33134,7 +33137,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -33169,7 +33172,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -33178,31 +33181,106 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="O176" t="n">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="P176" t="n">
-        <v>648</v>
-      </c>
-      <c r="R176" t="n">
-        <v>0.5292918481026165</v>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>669</v>
       </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN176" t="b">
+        <v>1</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
@@ -33301,17 +33379,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -33336,7 +33414,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -33345,178 +33423,81 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="O177" t="n">
-        <v>12</v>
-      </c>
-      <c r="P177" t="n">
-        <v>12</v>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE177" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN177" t="b">
+        <v>32</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0.009168122024862033</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="n">
         <v>0</v>
       </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP177" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT177" t="n">
-        <v>2</v>
-      </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33543,7 +33524,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -33595,98 +33576,23 @@
       <c r="P178" t="n">
         <v>648</v>
       </c>
+      <c r="R178" t="n">
+        <v>0.5292918481026165</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN178" t="b">
-        <v>1</v>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
@@ -33785,17 +33691,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -33820,104 +33726,187 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>187</v>
+        <v>12</v>
       </c>
       <c r="O179" t="n">
-        <v>187</v>
-      </c>
-      <c r="R179" t="n">
-        <v>0.6868158102502008</v>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="P179" t="n">
+        <v>12</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>0</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33949,12 +33938,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -33979,53 +33968,56 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>187</v>
+        <v>648</v>
       </c>
       <c r="O180" t="n">
-        <v>187</v>
+        <v>648</v>
+      </c>
+      <c r="P180" t="n">
+        <v>648</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>Varicella zoster (chickenpox)</t>
+          <t>Chickenpox</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>case_notifications</t>
+          <t>sentinel_case_notifications</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>sentinel_surveillance</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
@@ -34035,7 +34027,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr">
@@ -34075,12 +34067,12 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
         </is>
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -34088,70 +34080,75 @@
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34183,12 +34180,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -34222,38 +34219,55 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>10</v>
+        <v>187</v>
       </c>
       <c r="O181" t="n">
-        <v>10</v>
+        <v>187</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0.6868158102502008</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -34263,12 +34277,12 @@
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -34283,12 +34297,12 @@
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
@@ -34320,17 +34334,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -34364,38 +34378,130 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>187</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Varicella zoster (chickenpox)</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -34405,12 +34511,12 @@
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -34425,12 +34531,12 @@
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
@@ -34467,12 +34573,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -34506,10 +34612,10 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="O183" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -34547,7 +34653,7 @@
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
@@ -34567,7 +34673,7 @@
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
@@ -34609,12 +34715,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -34648,10 +34754,10 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -34689,7 +34795,7 @@
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
@@ -34709,7 +34815,7 @@
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
@@ -34751,12 +34857,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -34790,10 +34896,10 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="O185" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -34831,7 +34937,7 @@
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
@@ -34851,7 +34957,7 @@
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
@@ -34893,12 +34999,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -34932,10 +35038,10 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="O186" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -34973,7 +35079,7 @@
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
@@ -34993,7 +35099,7 @@
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
@@ -35035,12 +35141,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -35074,10 +35180,10 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="O187" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -35115,7 +35221,7 @@
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
@@ -35135,7 +35241,7 @@
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
@@ -35177,12 +35283,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -35216,20 +35322,14 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>30758</v>
+        <v>53</v>
       </c>
       <c r="O188" t="n">
-        <v>30758</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" t="n">
-        <v>2.17691933645122</v>
+        <v>53</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -35258,42 +35358,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35325,12 +35425,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -35364,17 +35464,14 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>1744</v>
+        <v>37</v>
       </c>
       <c r="O189" t="n">
-        <v>1744</v>
-      </c>
-      <c r="R189" t="n">
-        <v>3.379819547093328</v>
+        <v>37</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -35403,42 +35500,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35470,12 +35567,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -35509,13 +35606,16 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>37</v>
+        <v>30758</v>
       </c>
       <c r="O190" t="n">
-        <v>37</v>
+        <v>30758</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>0.01060064109124673</v>
+        <v>2.17691933645122</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -35548,42 +35648,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -35615,12 +35715,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35645,7 +35745,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -35654,103 +35754,81 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>594</v>
+        <v>1744</v>
       </c>
       <c r="O191" t="n">
-        <v>594</v>
-      </c>
-      <c r="P191" t="n">
-        <v>594</v>
+        <v>1744</v>
       </c>
       <c r="R191" t="n">
-        <v>0.4851841940940652</v>
+        <v>3.379819547093328</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35777,17 +35855,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35812,7 +35890,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -35821,178 +35899,81 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="O192" t="n">
-        <v>19</v>
-      </c>
-      <c r="P192" t="n">
-        <v>19</v>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
+        <v>37</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0.01060064109124673</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
+      <c r="AT192" t="n">
         <v>0</v>
       </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT192" t="n">
-        <v>2</v>
-      </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36019,7 +36000,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -36071,98 +36052,23 @@
       <c r="P193" t="n">
         <v>594</v>
       </c>
+      <c r="R193" t="n">
+        <v>0.4851841940940652</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U193" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN193" t="b">
-        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -36261,17 +36167,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -36296,7 +36202,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -36305,81 +36211,178 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="O194" t="n">
-        <v>41</v>
-      </c>
-      <c r="R194" t="n">
-        <v>0.01174665634435448</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="P194" t="n">
+        <v>19</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>0</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36406,7 +36409,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -36441,7 +36444,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -36450,31 +36453,106 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>555</v>
+        <v>594</v>
       </c>
       <c r="O195" t="n">
-        <v>555</v>
+        <v>594</v>
       </c>
       <c r="P195" t="n">
-        <v>555</v>
-      </c>
-      <c r="R195" t="n">
-        <v>0.4533286661990003</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>594</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -36573,17 +36651,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -36608,7 +36686,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -36617,178 +36695,81 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="O196" t="n">
-        <v>11</v>
-      </c>
-      <c r="P196" t="n">
-        <v>11</v>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
+        <v>41</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0.01174665634435448</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
+      <c r="AT196" t="n">
         <v>0</v>
       </c>
-      <c r="AO196" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP196" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT196" t="n">
-        <v>2</v>
-      </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36815,7 +36796,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -36867,98 +36848,23 @@
       <c r="P197" t="n">
         <v>555</v>
       </c>
+      <c r="R197" t="n">
+        <v>0.4533286661990003</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U197" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN197" t="b">
-        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
@@ -37057,17 +36963,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -37092,7 +36998,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -37101,81 +37007,178 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="O198" t="n">
-        <v>38</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0.01088714490452366</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="P198" t="n">
+        <v>11</v>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
+        <v>0</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37202,7 +37205,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -37237,7 +37240,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -37246,31 +37249,106 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>386</v>
+        <v>555</v>
       </c>
       <c r="O199" t="n">
-        <v>386</v>
+        <v>555</v>
       </c>
       <c r="P199" t="n">
-        <v>386</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0.3152880453203858</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>555</v>
       </c>
       <c r="U199" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -37369,17 +37447,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -37404,7 +37482,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -37413,178 +37491,81 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="O200" t="n">
-        <v>12</v>
-      </c>
-      <c r="P200" t="n">
-        <v>12</v>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
+        <v>38</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0.01088714490452366</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
+      <c r="AT200" t="n">
         <v>0</v>
       </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP200" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT200" t="n">
-        <v>2</v>
-      </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37611,7 +37592,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -37663,98 +37644,23 @@
       <c r="P201" t="n">
         <v>386</v>
       </c>
+      <c r="R201" t="n">
+        <v>0.3152880453203858</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -37853,17 +37759,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37888,7 +37794,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -37897,81 +37803,178 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="O202" t="n">
-        <v>43</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.01231966397090836</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="P202" t="n">
+        <v>12</v>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>0</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37998,7 +38001,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -38033,7 +38036,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -38042,31 +38045,106 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>589</v>
+        <v>386</v>
       </c>
       <c r="O203" t="n">
-        <v>589</v>
+        <v>386</v>
       </c>
       <c r="P203" t="n">
-        <v>589</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0.4811001520562364</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>386</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -38165,17 +38243,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -38200,7 +38278,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -38209,178 +38287,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="O204" t="n">
-        <v>11</v>
-      </c>
-      <c r="P204" t="n">
-        <v>11</v>
-      </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
+        <v>43</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0.01231966397090836</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
+      <c r="AT204" t="n">
         <v>0</v>
       </c>
-      <c r="AO204" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP204" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT204" t="n">
-        <v>2</v>
-      </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38407,7 +38388,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -38459,98 +38440,23 @@
       <c r="P205" t="n">
         <v>589</v>
       </c>
+      <c r="R205" t="n">
+        <v>0.4811001520562364</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -38649,17 +38555,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -38684,7 +38590,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -38693,81 +38599,178 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="O206" t="n">
-        <v>38</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0.01088714490452366</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="P206" t="n">
+        <v>11</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>0</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38794,7 +38797,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -38829,7 +38832,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -38838,31 +38841,106 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>433</v>
+        <v>589</v>
       </c>
       <c r="O207" t="n">
-        <v>433</v>
+        <v>589</v>
       </c>
       <c r="P207" t="n">
-        <v>433</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0.3536780404759768</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>589</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -38961,17 +39039,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38996,7 +39074,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -39005,178 +39083,81 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="O208" t="n">
-        <v>9</v>
-      </c>
-      <c r="P208" t="n">
-        <v>9</v>
-      </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
+        <v>38</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.01088714490452366</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="n">
         <v>0</v>
       </c>
-      <c r="AO208" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP208" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT208" t="n">
-        <v>2</v>
-      </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39203,7 +39184,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -39255,98 +39236,23 @@
       <c r="P209" t="n">
         <v>433</v>
       </c>
+      <c r="R209" t="n">
+        <v>0.3536780404759768</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U209" t="inlineStr">
         <is>
           <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Chickenpox</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -39445,17 +39351,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -39480,104 +39386,187 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N210" t="n">
+        <v>9</v>
+      </c>
+      <c r="O210" t="n">
+        <v>9</v>
+      </c>
+      <c r="P210" t="n">
+        <v>9</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT210" t="n">
         <v>2</v>
       </c>
-      <c r="O210" t="n">
-        <v>2</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0.007345623639039581</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO210" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP210" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="AT210" t="n">
-        <v>1</v>
-      </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39609,12 +39598,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -39639,53 +39628,56 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N211" t="n">
-        <v>2</v>
+        <v>433</v>
       </c>
       <c r="O211" t="n">
-        <v>2</v>
+        <v>433</v>
+      </c>
+      <c r="P211" t="n">
+        <v>433</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>Varicella zoster (chickenpox)</t>
+          <t>Chickenpox</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>case_notifications</t>
+          <t>sentinel_case_notifications</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>sentinel_surveillance</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
@@ -39695,7 +39687,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -39735,12 +39727,12 @@
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -39748,70 +39740,75 @@
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39843,12 +39840,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -39882,81 +39879,95 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>347</v>
+        <v>2</v>
       </c>
       <c r="O212" t="n">
-        <v>347</v>
+        <v>2</v>
       </c>
       <c r="R212" t="n">
-        <v>0.6724755635558399</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39983,123 +39994,502 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>2</v>
+      </c>
+      <c r="O213" t="n">
+        <v>2</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Varicella zoster (chickenpox)</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>347</v>
+      </c>
+      <c r="O214" t="n">
+        <v>347</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0.6724755635558399</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr"/>
+      <c r="AT214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA214" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB214" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC214" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>D054</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>Varicella</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
         <is>
           <t>水痘</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="K215" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N213" t="n">
+      <c r="N215" t="n">
         <v>41</v>
       </c>
-      <c r="O213" t="n">
+      <c r="O215" t="n">
         <v>41</v>
       </c>
-      <c r="R213" t="n">
+      <c r="R215" t="n">
         <v>0.01174665634435448</v>
       </c>
-      <c r="S213" t="inlineStr">
+      <c r="S215" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO213" t="inlineStr">
+      <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP213" t="inlineStr">
+      <c r="AP215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR213" t="inlineStr">
+      <c r="AR215" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS213" t="inlineStr"/>
-      <c r="AT213" t="n">
+      <c r="AS215" t="inlineStr"/>
+      <c r="AT215" t="n">
         <v>0</v>
       </c>
-      <c r="AU213" t="inlineStr">
+      <c r="AU215" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV213" t="inlineStr">
+      <c r="AV215" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW213" t="inlineStr">
+      <c r="AW215" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX213" t="inlineStr">
+      <c r="AX215" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY213" t="inlineStr">
+      <c r="AY215" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ213" t="inlineStr">
+      <c r="AZ215" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA213" t="inlineStr">
+      <c r="BA215" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB213" t="inlineStr">
+      <c r="BB215" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC213" t="inlineStr">
+      <c r="BC215" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -40221,7 +40611,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -40231,7 +40621,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -40251,7 +40641,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -40283,7 +40673,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>409446</v>
+        <v>409518</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -30890,13 +30890,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="O164" t="n">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="R164" t="n">
-        <v>4.86818044856562</v>
+        <v>4.870118418489412</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -35754,13 +35754,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="O191" t="n">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="R191" t="n">
-        <v>3.379819547093328</v>
+        <v>3.383695486940912</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -40272,13 +40272,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>347</v>
+        <v>414</v>
       </c>
       <c r="O214" t="n">
-        <v>347</v>
+        <v>414</v>
       </c>
       <c r="R214" t="n">
-        <v>0.6724755635558399</v>
+        <v>0.802319548449907</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>409518</v>
+        <v>409588</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -35754,13 +35754,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="O191" t="n">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="R191" t="n">
-        <v>3.383695486940912</v>
+        <v>3.389509396712288</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -40272,13 +40272,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>414</v>
+        <v>551</v>
       </c>
       <c r="O214" t="n">
-        <v>414</v>
+        <v>551</v>
       </c>
       <c r="R214" t="n">
-        <v>0.802319548449907</v>
+        <v>1.067821428009417</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -40492,6 +40492,657 @@
       <c r="BC215" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>476</v>
+      </c>
+      <c r="O216" t="n">
+        <v>476</v>
+      </c>
+      <c r="P216" t="n">
+        <v>476</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0.3888008020013047</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>13</v>
+      </c>
+      <c r="O217" t="n">
+        <v>13</v>
+      </c>
+      <c r="P217" t="n">
+        <v>13</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>476</v>
+      </c>
+      <c r="O218" t="n">
+        <v>476</v>
+      </c>
+      <c r="P218" t="n">
+        <v>476</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40528,7 +41179,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -40611,7 +41262,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -40621,7 +41272,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -40641,7 +41292,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -40673,7 +41324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>409588</v>
+        <v>410204</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -35754,13 +35754,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="O191" t="n">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="R191" t="n">
-        <v>3.389509396712288</v>
+        <v>3.393385336559872</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -40272,13 +40272,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>551</v>
+        <v>602</v>
       </c>
       <c r="O214" t="n">
-        <v>551</v>
+        <v>602</v>
       </c>
       <c r="R214" t="n">
-        <v>1.067821428009417</v>
+        <v>1.166657894122812</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>410204</v>
+        <v>410257</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -28820,13 +28820,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O151" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="R151" t="n">
-        <v>0.8227098475724329</v>
+        <v>0.8263826593919528</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -28979,10 +28979,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O152" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -30890,13 +30890,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="O164" t="n">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="R164" t="n">
-        <v>4.870118418489412</v>
+        <v>4.872056388413204</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -34219,13 +34219,13 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="O181" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="R181" t="n">
-        <v>0.6868158102502008</v>
+        <v>0.6978342457087601</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -34378,10 +34378,10 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="O182" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
@@ -35754,13 +35754,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="O191" t="n">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="R191" t="n">
-        <v>3.393385336559872</v>
+        <v>3.401137216255041</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -40272,13 +40272,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>602</v>
+        <v>753</v>
       </c>
       <c r="O214" t="n">
-        <v>602</v>
+        <v>753</v>
       </c>
       <c r="R214" t="n">
-        <v>1.166657894122812</v>
+        <v>1.459291352615411</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -41143,6 +41143,151 @@
       <c r="BC218" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>43</v>
+      </c>
+      <c r="O219" t="n">
+        <v>43</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.01231966397090836</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
+      <c r="AT219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41179,7 +41324,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -41262,7 +41407,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -41272,7 +41417,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11">
@@ -41324,7 +41469,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>410257</v>
+        <v>410460</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -40272,13 +40272,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>753</v>
+        <v>913</v>
       </c>
       <c r="O214" t="n">
-        <v>753</v>
+        <v>913</v>
       </c>
       <c r="R214" t="n">
-        <v>1.459291352615411</v>
+        <v>1.769366540422138</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -41469,7 +41469,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>410460</v>
+        <v>410620</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -13960,7 +13960,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -17344,7 +17344,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17901,7 +17901,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26275,7 +26275,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26829,7 +26829,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -27071,7 +27071,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27625,7 +27625,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28663,7 +28663,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29061,7 +29061,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31432,7 +31432,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32228,7 +32228,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33024,7 +33024,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -33820,7 +33820,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34062,7 +34062,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -34219,13 +34219,13 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="O181" t="n">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="R181" t="n">
-        <v>0.6978342457087601</v>
+        <v>0.9879863794508235</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -34378,10 +34378,10 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="O182" t="n">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35715,12 +35715,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35754,13 +35754,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1755</v>
+        <v>121</v>
       </c>
       <c r="O191" t="n">
-        <v>1755</v>
+        <v>121</v>
       </c>
       <c r="R191" t="n">
-        <v>3.401137216255041</v>
+        <v>1.639877039038018</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -35793,42 +35793,42 @@
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35860,12 +35860,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35899,13 +35899,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>37</v>
+        <v>1763</v>
       </c>
       <c r="O192" t="n">
-        <v>37</v>
+        <v>1763</v>
       </c>
       <c r="R192" t="n">
-        <v>0.01060064109124673</v>
+        <v>3.416640975645377</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -35938,42 +35938,42 @@
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -36005,12 +36005,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -36035,7 +36035,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -36044,103 +36044,81 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>594</v>
+        <v>37</v>
       </c>
       <c r="O193" t="n">
-        <v>594</v>
-      </c>
-      <c r="P193" t="n">
-        <v>594</v>
+        <v>37</v>
       </c>
       <c r="R193" t="n">
-        <v>0.4851841940940652</v>
+        <v>0.01060064109124673</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR193" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36167,7 +36145,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -36211,106 +36189,31 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>19</v>
+        <v>594</v>
       </c>
       <c r="O194" t="n">
-        <v>19</v>
+        <v>594</v>
       </c>
       <c r="P194" t="n">
-        <v>19</v>
+        <v>594</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0.4851841940940652</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>0</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -36453,22 +36356,22 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="O195" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="P195" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
@@ -36478,17 +36381,17 @@
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -36538,12 +36441,12 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM195" t="inlineStr">
@@ -36552,7 +36455,7 @@
         </is>
       </c>
       <c r="AN195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -36651,17 +36554,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -36686,7 +36589,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -36695,81 +36598,178 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>41</v>
+        <v>594</v>
       </c>
       <c r="O196" t="n">
-        <v>41</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0.01174665634435448</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>594</v>
+      </c>
+      <c r="P196" t="n">
+        <v>594</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR196" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36801,12 +36801,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36831,7 +36831,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -36840,103 +36840,81 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>555</v>
+        <v>41</v>
       </c>
       <c r="O197" t="n">
-        <v>555</v>
-      </c>
-      <c r="P197" t="n">
-        <v>555</v>
+        <v>41</v>
       </c>
       <c r="R197" t="n">
-        <v>0.4533286661990003</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36963,7 +36941,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -37007,106 +36985,31 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>11</v>
+        <v>555</v>
       </c>
       <c r="O198" t="n">
-        <v>11</v>
+        <v>555</v>
       </c>
       <c r="P198" t="n">
-        <v>11</v>
+        <v>555</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0.4533286661990003</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>0</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -37249,22 +37152,22 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="O199" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="P199" t="n">
-        <v>555</v>
+        <v>11</v>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
@@ -37274,17 +37177,17 @@
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -37334,12 +37237,12 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
@@ -37348,7 +37251,7 @@
         </is>
       </c>
       <c r="AN199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -37447,17 +37350,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -37482,7 +37385,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -37491,81 +37394,178 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>38</v>
+        <v>555</v>
       </c>
       <c r="O200" t="n">
-        <v>38</v>
-      </c>
-      <c r="R200" t="n">
-        <v>0.01088714490452366</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>555</v>
+      </c>
+      <c r="P200" t="n">
+        <v>555</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37597,12 +37597,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -37627,7 +37627,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -37636,103 +37636,81 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="O201" t="n">
-        <v>386</v>
-      </c>
-      <c r="P201" t="n">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="R201" t="n">
-        <v>0.3152880453203858</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37759,7 +37737,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -37803,106 +37781,31 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>12</v>
+        <v>386</v>
       </c>
       <c r="O202" t="n">
-        <v>12</v>
+        <v>386</v>
       </c>
       <c r="P202" t="n">
-        <v>12</v>
+        <v>386</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0.3152880453203858</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>0</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -38045,22 +37948,22 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>386</v>
+        <v>12</v>
       </c>
       <c r="O203" t="n">
-        <v>386</v>
+        <v>12</v>
       </c>
       <c r="P203" t="n">
-        <v>386</v>
+        <v>12</v>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
@@ -38070,17 +37973,17 @@
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -38130,12 +38033,12 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM203" t="inlineStr">
@@ -38144,7 +38047,7 @@
         </is>
       </c>
       <c r="AN203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -38243,17 +38146,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -38278,7 +38181,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -38287,81 +38190,178 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>43</v>
+        <v>386</v>
       </c>
       <c r="O204" t="n">
-        <v>43</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.01231966397090836</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>386</v>
+      </c>
+      <c r="P204" t="n">
+        <v>386</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR204" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38393,12 +38393,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -38423,7 +38423,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -38432,103 +38432,81 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>589</v>
+        <v>43</v>
       </c>
       <c r="O205" t="n">
-        <v>589</v>
-      </c>
-      <c r="P205" t="n">
-        <v>589</v>
+        <v>43</v>
       </c>
       <c r="R205" t="n">
-        <v>0.4811001520562364</v>
+        <v>0.01231966397090836</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR205" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38555,7 +38533,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -38599,106 +38577,31 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>11</v>
+        <v>589</v>
       </c>
       <c r="O206" t="n">
-        <v>11</v>
+        <v>589</v>
       </c>
       <c r="P206" t="n">
-        <v>11</v>
+        <v>589</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.4811001520562364</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>0</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -38841,22 +38744,22 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>589</v>
+        <v>11</v>
       </c>
       <c r="O207" t="n">
-        <v>589</v>
+        <v>11</v>
       </c>
       <c r="P207" t="n">
-        <v>589</v>
+        <v>11</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
@@ -38866,17 +38769,17 @@
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -38926,12 +38829,12 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -38940,7 +38843,7 @@
         </is>
       </c>
       <c r="AN207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
@@ -39039,17 +38942,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -39074,7 +38977,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -39083,81 +38986,178 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>38</v>
+        <v>589</v>
       </c>
       <c r="O208" t="n">
-        <v>38</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0.01088714490452366</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>589</v>
+      </c>
+      <c r="P208" t="n">
+        <v>589</v>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39189,12 +39189,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -39219,7 +39219,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -39228,103 +39228,81 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>433</v>
+        <v>38</v>
       </c>
       <c r="O209" t="n">
-        <v>433</v>
-      </c>
-      <c r="P209" t="n">
-        <v>433</v>
+        <v>38</v>
       </c>
       <c r="R209" t="n">
-        <v>0.3536780404759768</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39351,7 +39329,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -39395,106 +39373,31 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>9</v>
+        <v>433</v>
       </c>
       <c r="O210" t="n">
-        <v>9</v>
+        <v>433</v>
       </c>
       <c r="P210" t="n">
-        <v>9</v>
+        <v>433</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0.3536780404759768</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>0</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -39637,22 +39540,22 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>433</v>
+        <v>9</v>
       </c>
       <c r="O211" t="n">
-        <v>433</v>
+        <v>9</v>
       </c>
       <c r="P211" t="n">
-        <v>433</v>
+        <v>9</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
@@ -39662,17 +39565,17 @@
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -39722,12 +39625,12 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
@@ -39736,7 +39639,7 @@
         </is>
       </c>
       <c r="AN211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
@@ -39835,17 +39738,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -39870,104 +39773,187 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N212" t="n">
+        <v>433</v>
+      </c>
+      <c r="O212" t="n">
+        <v>433</v>
+      </c>
+      <c r="P212" t="n">
+        <v>433</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
         <v>2</v>
       </c>
-      <c r="O212" t="n">
-        <v>2</v>
-      </c>
-      <c r="R212" t="n">
-        <v>0.007345623639039581</v>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AP212" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="AT212" t="n">
-        <v>1</v>
-      </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39994,7 +39980,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -40043,98 +40029,23 @@
       <c r="O213" t="n">
         <v>2</v>
       </c>
+      <c r="R213" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U213" t="inlineStr">
         <is>
           <t>SER_AU_VARICELLA_CHICKENPOX</t>
         </is>
       </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>SER_AU_VARICELLA_CHICKENPOX</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>Varicella zoster (chickenpox)</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN213" t="b">
-        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
@@ -40228,17 +40139,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -40272,81 +40183,170 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>913</v>
+        <v>2</v>
       </c>
       <c r="O214" t="n">
-        <v>913</v>
-      </c>
-      <c r="R214" t="n">
-        <v>1.769366540422138</v>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Varicella zoster (chickenpox)</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Australia NINDSS chickenpox manifestation of VZV infection.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_AU_VARICELLA_CHICKENPOX</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -40378,12 +40378,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -40408,7 +40408,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -40417,13 +40417,13 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>41</v>
+        <v>1116</v>
       </c>
       <c r="O215" t="n">
-        <v>41</v>
+        <v>1116</v>
       </c>
       <c r="R215" t="n">
-        <v>0.01174665634435448</v>
+        <v>2.162774434951923</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -40456,42 +40456,42 @@
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -40523,12 +40523,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -40553,7 +40553,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -40562,103 +40562,81 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>476</v>
+        <v>41</v>
       </c>
       <c r="O216" t="n">
-        <v>476</v>
-      </c>
-      <c r="P216" t="n">
-        <v>476</v>
+        <v>41</v>
       </c>
       <c r="R216" t="n">
-        <v>0.3888008020013047</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR216" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40685,7 +40663,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -40729,106 +40707,31 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>13</v>
+        <v>476</v>
       </c>
       <c r="O217" t="n">
-        <v>13</v>
+        <v>476</v>
       </c>
       <c r="P217" t="n">
-        <v>13</v>
+        <v>476</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0.3888008020013047</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Chickenpox (hospitalized cases)</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>hospitalized_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>0</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
@@ -40971,22 +40874,22 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>476</v>
+        <v>13</v>
       </c>
       <c r="O218" t="n">
-        <v>476</v>
+        <v>13</v>
       </c>
       <c r="P218" t="n">
-        <v>476</v>
+        <v>13</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
@@ -40996,17 +40899,17 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>Chickenpox</t>
+          <t>Chickenpox (hospitalized cases)</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>sentinel_case_notifications</t>
+          <t>hospitalized_case_notifications</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>sentinel_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -41056,12 +40959,12 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
@@ -41070,7 +40973,7 @@
         </is>
       </c>
       <c r="AN218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
@@ -41169,123 +41072,1161 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>476</v>
+      </c>
+      <c r="O219" t="n">
+        <v>476</v>
+      </c>
+      <c r="P219" t="n">
+        <v>476</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G220" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>D054</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>Varicella</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
         <is>
           <t>水痘</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="K220" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="L220" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N219" t="n">
+      <c r="N220" t="n">
         <v>43</v>
       </c>
-      <c r="O219" t="n">
+      <c r="O220" t="n">
         <v>43</v>
       </c>
-      <c r="R219" t="n">
+      <c r="R220" t="n">
         <v>0.01231966397090836</v>
       </c>
-      <c r="S219" t="inlineStr">
+      <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO219" t="inlineStr">
+      <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP219" t="inlineStr">
+      <c r="AP220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR219" t="inlineStr">
+      <c r="AR220" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS219" t="inlineStr"/>
-      <c r="AT219" t="n">
+      <c r="AS220" t="inlineStr"/>
+      <c r="AT220" t="n">
         <v>0</v>
       </c>
-      <c r="AU219" t="inlineStr">
+      <c r="AU220" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV219" t="inlineStr">
+      <c r="AV220" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW219" t="inlineStr">
+      <c r="AW220" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX219" t="inlineStr">
+      <c r="AX220" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY219" t="inlineStr">
+      <c r="AY220" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ219" t="inlineStr">
+      <c r="AZ220" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA219" t="inlineStr">
+      <c r="BA220" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB219" t="inlineStr">
+      <c r="BB220" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC219" t="inlineStr">
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>369</v>
+      </c>
+      <c r="O221" t="n">
+        <v>369</v>
+      </c>
+      <c r="P221" t="n">
+        <v>369</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0.3014023023917677</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>9</v>
+      </c>
+      <c r="O222" t="n">
+        <v>9</v>
+      </c>
+      <c r="P222" t="n">
+        <v>9</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>369</v>
+      </c>
+      <c r="O223" t="n">
+        <v>369</v>
+      </c>
+      <c r="P223" t="n">
+        <v>369</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>47</v>
+      </c>
+      <c r="O224" t="n">
+        <v>47</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0.01346567922401611</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
+      <c r="AT224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -41324,7 +42265,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -41407,7 +42348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10">
@@ -41417,7 +42358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -41437,7 +42378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -41469,7 +42410,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>410620</v>
+        <v>411447</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -45029,13 +45029,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>2</v>
+        <v>165</v>
       </c>
       <c r="O239" t="n">
-        <v>2</v>
+        <v>165</v>
       </c>
       <c r="R239" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.6060139502207653</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -45188,10 +45188,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>2</v>
+        <v>165</v>
       </c>
       <c r="O240" t="n">
-        <v>2</v>
+        <v>165</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
@@ -45422,13 +45422,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>1116</v>
+        <v>1482</v>
       </c>
       <c r="O241" t="n">
-        <v>1116</v>
+        <v>1482</v>
       </c>
       <c r="R241" t="n">
-        <v>2.162774434951923</v>
+        <v>2.872071427059812</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -47234,6 +47234,947 @@
       <c r="BC250" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>496</v>
+      </c>
+      <c r="O251" t="n">
+        <v>496</v>
+      </c>
+      <c r="P251" t="n">
+        <v>496</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.4051369701526201</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV251" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA251" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB251" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC251" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N252" t="n">
+        <v>8</v>
+      </c>
+      <c r="O252" t="n">
+        <v>8</v>
+      </c>
+      <c r="P252" t="n">
+        <v>8</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_HOSPITALIZED_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Chickenpox (hospitalized cases)</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>hospitalized_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>Japan NIID hospitalized chickenpox cases only; not interchangeable with the sentinel chickenpox series.</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>496</v>
+      </c>
+      <c r="O253" t="n">
+        <v>496</v>
+      </c>
+      <c r="P253" t="n">
+        <v>496</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>Chickenpox</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Japan NIID chickenpox sentinel series, distinct from hospitalized-only reporting.</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN253" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>SER_JP_VARICELLA_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV253" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA253" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>45</v>
+      </c>
+      <c r="O254" t="n">
+        <v>45</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.01289267159746223</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr"/>
+      <c r="AT254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>varicella</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>33</v>
+      </c>
+      <c r="O255" t="n">
+        <v>33</v>
+      </c>
+      <c r="R255" t="n">
+        <v>0.06395300748513752</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr"/>
+      <c r="AT255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47270,7 +48211,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -47353,7 +48294,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -47363,7 +48304,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -47383,7 +48324,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -47415,7 +48356,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>428429</v>
+        <v>429532</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d054/2026-2029.xlsx
+++ b/diseases/d054/2026-2029.xlsx
@@ -37684,13 +37684,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O199" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R199" t="n">
-        <v>0.9879863794508235</v>
+        <v>0.9953320030898631</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -37843,10 +37843,10 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O200" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
@@ -45029,13 +45029,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="O239" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="R239" t="n">
-        <v>0.6060139502207653</v>
+        <v>0.6464148802354831</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -45188,10 +45188,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="O240" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
@@ -48356,7 +48356,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>429532</v>
+        <v>429545</v>
       </c>
     </row>
     <row r="16">
